--- a/human_resources_forms/014_employee_refusal_of_medical_treatment_form--human_resources_forms.xlsx
+++ b/human_resources_forms/014_employee_refusal_of_medical_treatment_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'i_understand_the_risks_of_refusal_of_medical_treatment',_'text':_'i_understand_the_risks_of_refusal_of_medical_treatment'}</t>
+          <t>i_understand_the_risks_of_refusal_of_medical_treatment</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'I understand the risks of refusal of medical treatment', 'text': 'I understand the risks of refusal of medical treatment'}</t>
+          <t>I understand the risks of refusal of medical treatment</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'i_do_not_understand_the_risks_of_refusal_of_medical_treatment',_'text':_'i_do_not_understand_the_risks_of_refusal_of_medical_treatment'}</t>
+          <t>i_do_not_understand_the_risks_of_refusal_of_medical_treatment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'I do not understand the risks of refusal of medical treatment', 'text': 'I do not understand the risks of refusal of medical treatment'}</t>
+          <t>I do not understand the risks of refusal of medical treatment</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'i_am_the_line_manager_for_this_employee',_'text':_'i_am_the_line_manager_for_this_employee'}</t>
+          <t>i_am_the_line_manager_for_this_employee</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'I am the line manager for this employee', 'text': 'I am the line manager for this employee'}</t>
+          <t>I am the line manager for this employee</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'i_am_not_the_line_manager_for_this_employee',_'text':_'i_am_not_the_line_manager_for_this_employee'}</t>
+          <t>i_am_not_the_line_manager_for_this_employee</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'I am not the line manager for this employee', 'text': 'I am not the line manager for this employee'}</t>
+          <t>I am not the line manager for this employee</t>
         </is>
       </c>
     </row>
